--- a/老虎机数学入门-PartV-触发率计算器.xlsx
+++ b/老虎机数学入门-PartV-触发率计算器.xlsx
@@ -5066,6 +5066,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:AO112" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6630,5 +6633,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:K95" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/老虎机数学入门-PartV-触发率计算器.xlsx
+++ b/老虎机数学入门-PartV-触发率计算器.xlsx
@@ -10,7 +10,7 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="PartV 五种触发率计算" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="175">
   <si>
     <t>老虎机数学入门 PART Ⅴ —— Feature 触发率计算器</t>
   </si>
@@ -1430,7 +1430,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1503,6 +1503,38 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2633,2409 +2665,2409 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:10">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="25" t="s">
+      <c r="B16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="25" t="s">
+      <c r="A17" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:10">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="25" t="s">
+      <c r="B18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:10">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="25" t="s">
+      <c r="B19" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="25" t="s">
+      <c r="B20" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="25" t="s">
+      <c r="A21" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:10">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G22" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="25" t="s">
+      <c r="B22" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="25" t="s">
+      <c r="B23" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="25" t="s">
+      <c r="A24" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1" spans="1:10">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D25" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="25" t="s">
+      <c r="F25" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="116" spans="1:10">
-      <c r="A26" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="32" t="s">
+      <c r="A26" s="46">
+        <v>1</v>
+      </c>
+      <c r="B26" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="33" t="s">
+      <c r="E26" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="25" t="s">
+      <c r="F26" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" ht="101.5" spans="1:10">
-      <c r="A27" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="32" t="s">
+      <c r="A27" s="46">
+        <v>2</v>
+      </c>
+      <c r="B27" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="33" t="s">
+      <c r="E27" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="25" t="s">
+      <c r="F27" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="87" spans="1:10">
-      <c r="A28" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="32" t="s">
+      <c r="A28" s="46">
+        <v>3</v>
+      </c>
+      <c r="B28" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="33" t="s">
+      <c r="E28" s="47" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="29" ht="72.5" spans="1:10">
-      <c r="A29" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="32" t="s">
+      <c r="A29" s="46">
+        <v>4</v>
+      </c>
+      <c r="B29" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="32" t="s">
+      <c r="C29" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="F29" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I29" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29" s="25" t="s">
+      <c r="F29" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I29" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="87" spans="1:10">
-      <c r="A30" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="32" t="s">
+      <c r="A30" s="46">
+        <v>5</v>
+      </c>
+      <c r="B30" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="E30" s="33" t="s">
+      <c r="E30" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="F30" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I30" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J30" s="25" t="s">
+      <c r="F30" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I30" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="72.5" spans="1:10">
-      <c r="A31" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="32" t="s">
+      <c r="A31" s="46">
+        <v>6</v>
+      </c>
+      <c r="B31" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="E31" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="F31" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I31" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J31" s="25" t="s">
+      <c r="F31" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I31" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" ht="72.5" spans="1:10">
-      <c r="A32" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="32" t="s">
+      <c r="A32" s="46">
+        <v>7</v>
+      </c>
+      <c r="B32" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="33" t="s">
+      <c r="E32" s="47" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="33" ht="101.5" spans="1:10">
-      <c r="A33" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="33" t="s">
+      <c r="A33" s="46">
+        <v>8</v>
+      </c>
+      <c r="B33" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="33" t="s">
+      <c r="E33" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="F33" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I33" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33" s="25" t="s">
+      <c r="F33" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="87" spans="1:10">
-      <c r="A34" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="32" t="s">
+      <c r="A34" s="46">
+        <v>9</v>
+      </c>
+      <c r="B34" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="E34" s="33" t="s">
+      <c r="E34" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="F34" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34" s="25" t="s">
+      <c r="F34" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="58" spans="1:10">
-      <c r="A35" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="32" t="s">
+      <c r="A35" s="46">
+        <v>10</v>
+      </c>
+      <c r="B35" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="33" t="s">
+      <c r="C35" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="E35" s="33" t="s">
+      <c r="E35" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G35" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I35" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35" s="25" t="s">
+      <c r="F35" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J36" s="25" t="s">
+      <c r="A36" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:10">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H37" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I37" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37" s="25" t="s">
+      <c r="B37" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H37" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I37" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:10">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H38" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I38" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J38" s="25" t="s">
+      <c r="B38" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G38" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H38" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I38" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:10">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="B39" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H39" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I39" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J39" s="25" t="s">
+      <c r="B39" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H39" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I39" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="B40" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H40" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I40" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40" s="25" t="s">
+      <c r="B40" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H40" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I40" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H41" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I41" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41" s="25" t="s">
+      <c r="A41" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A42" s="34" t="s">
+      <c r="A42" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I42" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42" s="25" t="s">
+      <c r="B42" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H42" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:10">
-      <c r="A43" s="35" t="s">
+      <c r="A43" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H43" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I43" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43" s="25" t="s">
+      <c r="B43" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H43" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:10">
-      <c r="A44" s="35" t="s">
+      <c r="A44" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="B44" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I44" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44" s="25" t="s">
+      <c r="B44" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:10">
-      <c r="A45" s="35" t="s">
+      <c r="A45" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="B45" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H45" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I45" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45" s="25" t="s">
+      <c r="B45" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:10">
-      <c r="A46" s="35" t="s">
+      <c r="A46" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="B46" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H46" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I46" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46" s="25" t="s">
+      <c r="B46" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H46" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I46" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A47" s="34" t="s">
+      <c r="A47" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="B47" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I47" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="25" t="s">
+      <c r="B47" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:10">
-      <c r="A48" s="35" t="s">
+      <c r="A48" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="B48" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H48" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I48" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J48" s="25" t="s">
+      <c r="B48" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I48" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:10">
-      <c r="A49" s="35" t="s">
+      <c r="A49" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="B49" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E49" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H49" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I49" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J49" s="25" t="s">
+      <c r="B49" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E49" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I49" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A50" s="34" t="s">
+      <c r="A50" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="B50" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H50" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I50" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50" s="25" t="s">
+      <c r="B50" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:10">
-      <c r="A51" s="29" t="s">
+      <c r="A51" s="43" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:10">
-      <c r="A52" s="35" t="s">
+      <c r="A52" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="B52" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G52" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H52" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I52" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52" s="25" t="s">
+      <c r="B52" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I52" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:10">
-      <c r="A53" s="35" t="s">
+      <c r="A53" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="B53" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I53" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53" s="25" t="s">
+      <c r="B53" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I53" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:10">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="B54" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C54" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G54" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H54" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I54" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54" s="25" t="s">
+      <c r="B54" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I54" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:10">
-      <c r="A55" s="35" t="s">
+      <c r="A55" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="B55" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F55" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G55" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H55" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I55" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J55" s="25" t="s">
+      <c r="B55" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G55" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H55" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I55" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J55" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A56" s="34" t="s">
+      <c r="A56" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="B56" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D56" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E56" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F56" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G56" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H56" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I56" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J56" s="25" t="s">
+      <c r="B56" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D56" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G56" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H56" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I56" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J56" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:10">
-      <c r="A57" s="35" t="s">
+      <c r="A57" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="B57" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E57" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I57" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J57" s="25" t="s">
+      <c r="B57" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I57" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J57" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:10">
-      <c r="A58" s="35" t="s">
+      <c r="A58" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="B58" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F58" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H58" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I58" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J58" s="25" t="s">
+      <c r="B58" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H58" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I58" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J58" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A59" s="34" t="s">
+      <c r="A59" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="B59" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C59" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E59" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F59" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G59" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H59" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I59" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J59" s="25" t="s">
+      <c r="B59" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E59" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H59" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I59" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J59" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:10">
-      <c r="A60" s="35" t="s">
+      <c r="A60" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="B60" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E60" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H60" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I60" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J60" s="25" t="s">
+      <c r="B60" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E60" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H60" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I60" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J60" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:10">
-      <c r="A61" s="35" t="s">
+      <c r="A61" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B61" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E61" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H61" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I61" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J61" s="25" t="s">
+      <c r="B61" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H61" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I61" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:10">
-      <c r="A62" s="35" t="s">
+      <c r="A62" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="B62" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E62" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G62" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H62" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I62" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J62" s="25" t="s">
+      <c r="B62" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E62" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H62" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I62" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J62" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:10">
-      <c r="A63" s="35" t="s">
+      <c r="A63" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="B63" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G63" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H63" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I63" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J63" s="25" t="s">
+      <c r="B63" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H63" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I63" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="64" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="B64" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E64" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G64" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H64" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I64" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J64" s="25" t="s">
+      <c r="B64" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G64" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H64" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I64" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J64" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B65" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E65" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H65" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I65" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J65" s="25" t="s">
+      <c r="A65" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B65" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H65" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I65" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J65" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="66" ht="45" customHeight="1" spans="1:10">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="B66" s="30" t="s">
+      <c r="B66" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="31" t="s">
+      <c r="C66" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="D66" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E66" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G66" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H66" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I66" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J66" s="25" t="s">
+      <c r="D66" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G66" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H66" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I66" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J66" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="67" ht="58" spans="1:10">
-      <c r="A67" s="32" t="s">
+      <c r="A67" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="B67" s="36" t="s">
+      <c r="B67" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="C67" s="37" t="s">
+      <c r="C67" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="D67" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E67" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G67" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H67" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I67" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J67" s="25" t="s">
+      <c r="D67" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H67" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I67" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J67" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="68" ht="58" spans="1:10">
-      <c r="A68" s="32" t="s">
+      <c r="A68" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="B68" s="36" t="s">
+      <c r="B68" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="C68" s="37" t="s">
+      <c r="C68" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="D68" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E68" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G68" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H68" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I68" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J68" s="25" t="s">
+      <c r="D68" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E68" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G68" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H68" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I68" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J68" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" ht="29" spans="1:10">
-      <c r="A69" s="32" t="s">
+      <c r="A69" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="B69" s="36" t="s">
+      <c r="B69" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="C69" s="37" t="s">
+      <c r="C69" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="D69" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E69" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F69" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G69" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H69" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I69" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J69" s="25" t="s">
+      <c r="D69" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E69" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G69" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H69" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I69" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J69" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="70" ht="29" spans="1:10">
-      <c r="A70" s="32" t="s">
+      <c r="A70" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="B70" s="36" t="s">
+      <c r="B70" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="C70" s="37" t="s">
+      <c r="C70" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="D70" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E70" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G70" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H70" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I70" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J70" s="25" t="s">
+      <c r="D70" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E70" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G70" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H70" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I70" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J70" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="71" ht="14.5" spans="1:10">
-      <c r="A71" s="32" t="s">
+      <c r="A71" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="B71" s="33" t="s">
+      <c r="B71" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="C71" s="33" t="s">
+      <c r="C71" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="D71" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E71" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G71" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H71" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I71" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J71" s="25" t="s">
+      <c r="D71" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E71" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G71" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H71" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I71" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J71" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B72" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E72" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F72" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G72" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H72" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I72" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J72" s="25" t="s">
+      <c r="A72" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B72" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D72" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E72" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G72" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H72" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I72" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J72" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A73" s="28" t="s">
+      <c r="A73" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="B73" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C73" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D73" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E73" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F73" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G73" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H73" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I73" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J73" s="25" t="s">
+      <c r="B73" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G73" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H73" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I73" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J73" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B74" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D74" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E74" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F74" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G74" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H74" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I74" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J74" s="25" t="s">
+      <c r="A74" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B74" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D74" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E74" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G74" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H74" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I74" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J74" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:10">
-      <c r="A75" s="35" t="s">
+      <c r="A75" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="B75" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D75" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E75" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F75" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G75" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H75" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I75" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J75" s="25" t="s">
+      <c r="B75" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E75" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G75" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H75" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I75" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J75" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" spans="1:10">
-      <c r="A76" s="30" t="s">
+      <c r="A76" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B76" s="31" t="s">
+      <c r="B76" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="C76" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D76" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E76" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F76" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G76" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H76" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I76" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J76" s="25" t="s">
+      <c r="C76" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D76" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E76" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G76" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H76" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I76" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J76" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" ht="14.5" spans="1:10">
-      <c r="A77" s="32" t="s">
+      <c r="A77" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="B77" s="33" t="s">
+      <c r="B77" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="C77" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D77" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E77" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F77" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G77" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H77" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I77" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J77" s="25" t="s">
+      <c r="C77" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D77" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E77" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G77" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H77" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I77" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J77" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="78" ht="14.5" spans="1:10">
-      <c r="A78" s="32" t="s">
+      <c r="A78" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="B78" s="33" t="s">
+      <c r="B78" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="C78" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D78" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E78" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F78" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G78" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H78" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I78" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J78" s="25" t="s">
+      <c r="C78" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E78" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F78" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G78" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H78" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I78" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J78" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B79" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D79" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E79" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F79" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G79" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H79" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I79" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J79" s="25" t="s">
+      <c r="A79" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B79" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C79" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D79" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E79" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G79" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H79" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I79" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J79" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A80" s="28" t="s">
+      <c r="A80" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="B80" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C80" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D80" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E80" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F80" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G80" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H80" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I80" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J80" s="25" t="s">
+      <c r="B80" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D80" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E80" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G80" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H80" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I80" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J80" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B81" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C81" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D81" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E81" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F81" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G81" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H81" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I81" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J81" s="25" t="s">
+      <c r="A81" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B81" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C81" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D81" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E81" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G81" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H81" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I81" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J81" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1" spans="1:10">
-      <c r="A82" s="30" t="s">
+      <c r="A82" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="B82" s="31" t="s">
+      <c r="B82" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="C82" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E82" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F82" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G82" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H82" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I82" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J82" s="25" t="s">
+      <c r="C82" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D82" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E82" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G82" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H82" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I82" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J82" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="83" ht="14.5" spans="1:10">
-      <c r="A83" s="32" t="s">
+      <c r="A83" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="B83" s="33" t="s">
+      <c r="B83" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="C83" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D83" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E83" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F83" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G83" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H83" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I83" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J83" s="25" t="s">
+      <c r="C83" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D83" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E83" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F83" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G83" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H83" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I83" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J83" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="84" ht="14.5" spans="1:10">
-      <c r="A84" s="32" t="s">
+      <c r="A84" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="B84" s="33" t="s">
+      <c r="B84" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="C84" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D84" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E84" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F84" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G84" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H84" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I84" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J84" s="25" t="s">
+      <c r="C84" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E84" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G84" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H84" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I84" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J84" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="85" ht="14.5" spans="1:10">
-      <c r="A85" s="32" t="s">
+      <c r="A85" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="B85" s="33" t="s">
+      <c r="B85" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="C85" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D85" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E85" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F85" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G85" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H85" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I85" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J85" s="25" t="s">
+      <c r="C85" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D85" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G85" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H85" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I85" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J85" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="86" ht="14.5" spans="1:10">
-      <c r="A86" s="32" t="s">
+      <c r="A86" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="B86" s="33" t="s">
+      <c r="B86" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="C86" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D86" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E86" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F86" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G86" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H86" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I86" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J86" s="25" t="s">
+      <c r="C86" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D86" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E86" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G86" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H86" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I86" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J86" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="87" ht="14.5" spans="1:10">
-      <c r="A87" s="32" t="s">
+      <c r="A87" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="B87" s="33" t="s">
+      <c r="B87" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="C87" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D87" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E87" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F87" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G87" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H87" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I87" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J87" s="25" t="s">
+      <c r="C87" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D87" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E87" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G87" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H87" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I87" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J87" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B88" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C88" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D88" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E88" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F88" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G88" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H88" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I88" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J88" s="25" t="s">
+      <c r="A88" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B88" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D88" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E88" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G88" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H88" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I88" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J88" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A89" s="28" t="s">
+      <c r="A89" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="B89" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C89" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D89" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E89" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F89" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G89" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H89" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I89" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J89" s="25" t="s">
+      <c r="B89" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E89" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F89" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G89" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H89" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I89" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J89" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B90" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C90" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D90" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E90" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F90" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G90" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H90" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I90" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J90" s="25" t="s">
+      <c r="A90" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B90" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C90" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D90" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E90" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F90" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G90" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H90" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I90" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J90" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:10">
-      <c r="A91" s="35" t="s">
+      <c r="A91" s="49" t="s">
         <v>121</v>
       </c>
-      <c r="B91" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C91" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D91" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E91" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F91" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G91" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H91" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I91" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J91" s="25" t="s">
+      <c r="B91" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D91" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E91" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F91" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G91" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H91" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I91" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J91" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:10">
-      <c r="A92" s="35" t="s">
+      <c r="A92" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="B92" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C92" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D92" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E92" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F92" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G92" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H92" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="I92" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J92" s="25" t="s">
+      <c r="B92" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C92" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D92" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="E92" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F92" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G92" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="H92" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="I92" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J92" s="39" t="s">
         <v>1</v>
       </c>
     </row>
